--- a/testing/results/stage2_dispatch_2020-01-27.xlsx
+++ b/testing/results/stage2_dispatch_2020-01-27.xlsx
@@ -810,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ165"/>
+  <dimension ref="A1:AZ174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26864,462 +26864,1560 @@
     <row r="163">
       <c r="A163" s="14" t="inlineStr">
         <is>
-          <t>Reg Up Available (MW)</t>
+          <t>ED Cost per Period ($)</t>
         </is>
       </c>
       <c r="B163" s="15" t="n"/>
       <c r="C163" s="15" t="n"/>
       <c r="D163" s="15" t="n"/>
-      <c r="E163" s="16" t="n">
-        <v>1443.6</v>
-      </c>
-      <c r="F163" s="16" t="n">
-        <v>1213.4</v>
-      </c>
-      <c r="G163" s="16" t="n">
-        <v>1266.4</v>
-      </c>
-      <c r="H163" s="16" t="n">
-        <v>1344.4</v>
-      </c>
-      <c r="I163" s="16" t="n">
-        <v>1043.3</v>
-      </c>
-      <c r="J163" s="16" t="n">
-        <v>548.9</v>
-      </c>
-      <c r="K163" s="16" t="n">
-        <v>1134.9</v>
-      </c>
-      <c r="L163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U163" s="16" t="n">
-        <v>1302.4</v>
-      </c>
-      <c r="V163" s="16" t="n">
-        <v>1365.4</v>
-      </c>
-      <c r="W163" s="16" t="n">
-        <v>1644.9</v>
-      </c>
-      <c r="X163" s="16" t="n">
-        <v>1751.5</v>
-      </c>
-      <c r="Y163" s="16" t="n">
-        <v>1732.5</v>
-      </c>
-      <c r="Z163" s="16" t="n">
-        <v>1669.7</v>
-      </c>
-      <c r="AA163" s="16" t="n">
-        <v>1812.4</v>
-      </c>
-      <c r="AB163" s="16" t="n">
-        <v>1354.9</v>
-      </c>
-      <c r="AC163" s="16" t="n">
-        <v>1363.1</v>
-      </c>
-      <c r="AD163" s="16" t="n">
-        <v>1513.1</v>
-      </c>
-      <c r="AE163" s="16" t="n">
-        <v>1313.4</v>
-      </c>
-      <c r="AF163" s="16" t="n">
-        <v>1011.9</v>
-      </c>
-      <c r="AG163" s="16" t="n">
-        <v>1073.2</v>
-      </c>
-      <c r="AH163" s="16" t="n">
-        <v>1033.1</v>
-      </c>
-      <c r="AI163" s="16" t="n">
-        <v>1146</v>
-      </c>
-      <c r="AJ163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR163" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS163" s="16" t="n">
-        <v>1162.3</v>
-      </c>
-      <c r="AT163" s="16" t="n">
-        <v>1342.7</v>
-      </c>
-      <c r="AU163" s="16" t="n">
-        <v>1469.6</v>
-      </c>
-      <c r="AV163" s="16" t="n">
-        <v>1361.1</v>
-      </c>
-      <c r="AW163" s="16" t="n">
-        <v>1834.5</v>
-      </c>
-      <c r="AX163" s="16" t="n">
-        <v>1658.7</v>
-      </c>
-      <c r="AY163" s="16" t="n">
-        <v>1753.7</v>
-      </c>
-      <c r="AZ163" s="16" t="n">
-        <v>1548.8</v>
-      </c>
+      <c r="E163" s="16" t="n"/>
+      <c r="F163" s="16" t="n"/>
+      <c r="G163" s="16" t="n"/>
+      <c r="H163" s="16" t="n"/>
+      <c r="I163" s="16" t="n"/>
+      <c r="J163" s="16" t="n"/>
+      <c r="K163" s="16" t="n"/>
+      <c r="L163" s="16" t="n"/>
+      <c r="M163" s="16" t="n"/>
+      <c r="N163" s="16" t="n"/>
+      <c r="O163" s="16" t="n"/>
+      <c r="P163" s="16" t="n"/>
+      <c r="Q163" s="16" t="n"/>
+      <c r="R163" s="16" t="n"/>
+      <c r="S163" s="16" t="n"/>
+      <c r="T163" s="16" t="n"/>
+      <c r="U163" s="16" t="n"/>
+      <c r="V163" s="16" t="n"/>
+      <c r="W163" s="16" t="n"/>
+      <c r="X163" s="16" t="n"/>
+      <c r="Y163" s="16" t="n"/>
+      <c r="Z163" s="16" t="n"/>
+      <c r="AA163" s="16" t="n"/>
+      <c r="AB163" s="16" t="n"/>
+      <c r="AC163" s="16" t="n"/>
+      <c r="AD163" s="16" t="n"/>
+      <c r="AE163" s="16" t="n"/>
+      <c r="AF163" s="16" t="n"/>
+      <c r="AG163" s="16" t="n"/>
+      <c r="AH163" s="16" t="n"/>
+      <c r="AI163" s="16" t="n"/>
+      <c r="AJ163" s="16" t="n"/>
+      <c r="AK163" s="16" t="n"/>
+      <c r="AL163" s="16" t="n"/>
+      <c r="AM163" s="16" t="n"/>
+      <c r="AN163" s="16" t="n"/>
+      <c r="AO163" s="16" t="n"/>
+      <c r="AP163" s="16" t="n"/>
+      <c r="AQ163" s="16" t="n"/>
+      <c r="AR163" s="16" t="n"/>
+      <c r="AS163" s="16" t="n"/>
+      <c r="AT163" s="16" t="n"/>
+      <c r="AU163" s="16" t="n"/>
+      <c r="AV163" s="16" t="n"/>
+      <c r="AW163" s="16" t="n"/>
+      <c r="AX163" s="16" t="n"/>
+      <c r="AY163" s="16" t="n"/>
+      <c r="AZ163" s="16" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>Reg Down Available (MW)</t>
+          <t>Startup Cost per Period ($)</t>
         </is>
       </c>
       <c r="B164" s="15" t="n"/>
       <c r="C164" s="15" t="n"/>
       <c r="D164" s="15" t="n"/>
-      <c r="E164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" s="16" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="G164" s="16" t="n">
-        <v>181</v>
-      </c>
-      <c r="H164" s="16" t="n">
-        <v>228.4</v>
-      </c>
-      <c r="I164" s="16" t="n">
-        <v>378.6</v>
-      </c>
-      <c r="J164" s="16" t="n">
-        <v>665.2</v>
-      </c>
-      <c r="K164" s="16" t="n">
-        <v>397.9</v>
-      </c>
-      <c r="L164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U164" s="16" t="n">
-        <v>260.1</v>
-      </c>
-      <c r="V164" s="16" t="n">
-        <v>614.6</v>
-      </c>
-      <c r="W164" s="16" t="n">
-        <v>452.7</v>
-      </c>
-      <c r="X164" s="16" t="n">
-        <v>310.1</v>
-      </c>
-      <c r="Y164" s="16" t="n">
-        <v>189.5</v>
-      </c>
-      <c r="Z164" s="16" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="AA164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB164" s="16" t="n">
-        <v>233.2</v>
-      </c>
-      <c r="AC164" s="16" t="n">
-        <v>157.1</v>
-      </c>
-      <c r="AD164" s="16" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="AE164" s="16" t="n">
-        <v>131.1</v>
-      </c>
-      <c r="AF164" s="16" t="n">
-        <v>322.7</v>
-      </c>
-      <c r="AG164" s="16" t="n">
-        <v>261.7</v>
-      </c>
-      <c r="AH164" s="16" t="n">
-        <v>346.4</v>
-      </c>
-      <c r="AI164" s="16" t="n">
-        <v>509</v>
-      </c>
-      <c r="AJ164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS164" s="16" t="n">
-        <v>738</v>
-      </c>
-      <c r="AT164" s="16" t="n">
-        <v>704.8</v>
-      </c>
-      <c r="AU164" s="16" t="n">
-        <v>608.5</v>
-      </c>
-      <c r="AV164" s="16" t="n">
-        <v>787.7</v>
-      </c>
-      <c r="AW164" s="16" t="n">
-        <v>260.6</v>
-      </c>
-      <c r="AX164" s="16" t="n">
-        <v>207.6</v>
-      </c>
-      <c r="AY164" s="16" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="AZ164" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E164" s="16" t="n"/>
+      <c r="F164" s="16" t="n"/>
+      <c r="G164" s="16" t="n"/>
+      <c r="H164" s="16" t="n"/>
+      <c r="I164" s="16" t="n"/>
+      <c r="J164" s="16" t="n"/>
+      <c r="K164" s="16" t="n"/>
+      <c r="L164" s="16" t="n"/>
+      <c r="M164" s="16" t="n"/>
+      <c r="N164" s="16" t="n"/>
+      <c r="O164" s="16" t="n"/>
+      <c r="P164" s="16" t="n"/>
+      <c r="Q164" s="16" t="n"/>
+      <c r="R164" s="16" t="n"/>
+      <c r="S164" s="16" t="n"/>
+      <c r="T164" s="16" t="n"/>
+      <c r="U164" s="16" t="n"/>
+      <c r="V164" s="16" t="n"/>
+      <c r="W164" s="16" t="n"/>
+      <c r="X164" s="16" t="n"/>
+      <c r="Y164" s="16" t="n"/>
+      <c r="Z164" s="16" t="n"/>
+      <c r="AA164" s="16" t="n"/>
+      <c r="AB164" s="16" t="n"/>
+      <c r="AC164" s="16" t="n"/>
+      <c r="AD164" s="16" t="n"/>
+      <c r="AE164" s="16" t="n"/>
+      <c r="AF164" s="16" t="n"/>
+      <c r="AG164" s="16" t="n"/>
+      <c r="AH164" s="16" t="n"/>
+      <c r="AI164" s="16" t="n"/>
+      <c r="AJ164" s="16" t="n"/>
+      <c r="AK164" s="16" t="n"/>
+      <c r="AL164" s="16" t="n"/>
+      <c r="AM164" s="16" t="n"/>
+      <c r="AN164" s="16" t="n"/>
+      <c r="AO164" s="16" t="n"/>
+      <c r="AP164" s="16" t="n"/>
+      <c r="AQ164" s="16" t="n"/>
+      <c r="AR164" s="16" t="n"/>
+      <c r="AS164" s="16" t="n"/>
+      <c r="AT164" s="16" t="n"/>
+      <c r="AU164" s="16" t="n"/>
+      <c r="AV164" s="16" t="n"/>
+      <c r="AW164" s="16" t="n"/>
+      <c r="AX164" s="16" t="n"/>
+      <c r="AY164" s="16" t="n"/>
+      <c r="AZ164" s="16" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="14" t="inlineStr">
         <is>
-          <t>Total Dispatch (MW)</t>
+          <t>Total Cost per Period ($)</t>
         </is>
       </c>
       <c r="B165" s="15" t="n"/>
       <c r="C165" s="15" t="n"/>
       <c r="D165" s="15" t="n"/>
-      <c r="E165" s="16" t="n">
+      <c r="E165" s="16" t="n"/>
+      <c r="F165" s="16" t="n"/>
+      <c r="G165" s="16" t="n"/>
+      <c r="H165" s="16" t="n"/>
+      <c r="I165" s="16" t="n"/>
+      <c r="J165" s="16" t="n"/>
+      <c r="K165" s="16" t="n"/>
+      <c r="L165" s="16" t="n"/>
+      <c r="M165" s="16" t="n"/>
+      <c r="N165" s="16" t="n"/>
+      <c r="O165" s="16" t="n"/>
+      <c r="P165" s="16" t="n"/>
+      <c r="Q165" s="16" t="n"/>
+      <c r="R165" s="16" t="n"/>
+      <c r="S165" s="16" t="n"/>
+      <c r="T165" s="16" t="n"/>
+      <c r="U165" s="16" t="n"/>
+      <c r="V165" s="16" t="n"/>
+      <c r="W165" s="16" t="n"/>
+      <c r="X165" s="16" t="n"/>
+      <c r="Y165" s="16" t="n"/>
+      <c r="Z165" s="16" t="n"/>
+      <c r="AA165" s="16" t="n"/>
+      <c r="AB165" s="16" t="n"/>
+      <c r="AC165" s="16" t="n"/>
+      <c r="AD165" s="16" t="n"/>
+      <c r="AE165" s="16" t="n"/>
+      <c r="AF165" s="16" t="n"/>
+      <c r="AG165" s="16" t="n"/>
+      <c r="AH165" s="16" t="n"/>
+      <c r="AI165" s="16" t="n"/>
+      <c r="AJ165" s="16" t="n"/>
+      <c r="AK165" s="16" t="n"/>
+      <c r="AL165" s="16" t="n"/>
+      <c r="AM165" s="16" t="n"/>
+      <c r="AN165" s="16" t="n"/>
+      <c r="AO165" s="16" t="n"/>
+      <c r="AP165" s="16" t="n"/>
+      <c r="AQ165" s="16" t="n"/>
+      <c r="AR165" s="16" t="n"/>
+      <c r="AS165" s="16" t="n"/>
+      <c r="AT165" s="16" t="n"/>
+      <c r="AU165" s="16" t="n"/>
+      <c r="AV165" s="16" t="n"/>
+      <c r="AW165" s="16" t="n"/>
+      <c r="AX165" s="16" t="n"/>
+      <c r="AY165" s="16" t="n"/>
+      <c r="AZ165" s="16" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="14" t="inlineStr">
+        <is>
+          <t>Reg Up Available (MW)</t>
+        </is>
+      </c>
+      <c r="B166" s="15" t="n"/>
+      <c r="C166" s="15" t="n"/>
+      <c r="D166" s="15" t="n"/>
+      <c r="E166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ166" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="14" t="inlineStr">
+        <is>
+          <t>Reg Down Available (MW)</t>
+        </is>
+      </c>
+      <c r="B167" s="15" t="n"/>
+      <c r="C167" s="15" t="n"/>
+      <c r="D167" s="15" t="n"/>
+      <c r="E167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ167" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="14" t="inlineStr">
+        <is>
+          <t>Spin Up Available (MW)</t>
+        </is>
+      </c>
+      <c r="B168" s="15" t="n"/>
+      <c r="C168" s="15" t="n"/>
+      <c r="D168" s="15" t="n"/>
+      <c r="E168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ168" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="14" t="inlineStr">
+        <is>
+          <t>Spin Down Available (MW)</t>
+        </is>
+      </c>
+      <c r="B169" s="15" t="n"/>
+      <c r="C169" s="15" t="n"/>
+      <c r="D169" s="15" t="n"/>
+      <c r="E169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ169" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="14" t="inlineStr">
+        <is>
+          <t>Flex Up Available (MW)</t>
+        </is>
+      </c>
+      <c r="B170" s="15" t="n"/>
+      <c r="C170" s="15" t="n"/>
+      <c r="D170" s="15" t="n"/>
+      <c r="E170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ170" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="14" t="inlineStr">
+        <is>
+          <t>Flex Down Available (MW)</t>
+        </is>
+      </c>
+      <c r="B171" s="15" t="n"/>
+      <c r="C171" s="15" t="n"/>
+      <c r="D171" s="15" t="n"/>
+      <c r="E171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ171" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="14" t="inlineStr">
+        <is>
+          <t>Ramp Up Available (MW)</t>
+        </is>
+      </c>
+      <c r="B172" s="15" t="n"/>
+      <c r="C172" s="15" t="n"/>
+      <c r="D172" s="15" t="n"/>
+      <c r="E172" s="16" t="n">
+        <v>1443.6</v>
+      </c>
+      <c r="F172" s="16" t="n">
+        <v>1213.4</v>
+      </c>
+      <c r="G172" s="16" t="n">
+        <v>1266.4</v>
+      </c>
+      <c r="H172" s="16" t="n">
+        <v>1344.4</v>
+      </c>
+      <c r="I172" s="16" t="n">
+        <v>1043.3</v>
+      </c>
+      <c r="J172" s="16" t="n">
+        <v>548.9</v>
+      </c>
+      <c r="K172" s="16" t="n">
+        <v>1134.9</v>
+      </c>
+      <c r="L172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" s="16" t="n">
+        <v>1302.4</v>
+      </c>
+      <c r="V172" s="16" t="n">
+        <v>1365.4</v>
+      </c>
+      <c r="W172" s="16" t="n">
+        <v>1644.9</v>
+      </c>
+      <c r="X172" s="16" t="n">
+        <v>1751.5</v>
+      </c>
+      <c r="Y172" s="16" t="n">
+        <v>1732.5</v>
+      </c>
+      <c r="Z172" s="16" t="n">
+        <v>1669.7</v>
+      </c>
+      <c r="AA172" s="16" t="n">
+        <v>1812.4</v>
+      </c>
+      <c r="AB172" s="16" t="n">
+        <v>1354.9</v>
+      </c>
+      <c r="AC172" s="16" t="n">
+        <v>1363.1</v>
+      </c>
+      <c r="AD172" s="16" t="n">
+        <v>1513.1</v>
+      </c>
+      <c r="AE172" s="16" t="n">
+        <v>1313.4</v>
+      </c>
+      <c r="AF172" s="16" t="n">
+        <v>1011.9</v>
+      </c>
+      <c r="AG172" s="16" t="n">
+        <v>1073.2</v>
+      </c>
+      <c r="AH172" s="16" t="n">
+        <v>1033.1</v>
+      </c>
+      <c r="AI172" s="16" t="n">
+        <v>1146</v>
+      </c>
+      <c r="AJ172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR172" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS172" s="16" t="n">
+        <v>1162.3</v>
+      </c>
+      <c r="AT172" s="16" t="n">
+        <v>1342.7</v>
+      </c>
+      <c r="AU172" s="16" t="n">
+        <v>1469.6</v>
+      </c>
+      <c r="AV172" s="16" t="n">
+        <v>1361.1</v>
+      </c>
+      <c r="AW172" s="16" t="n">
+        <v>1834.5</v>
+      </c>
+      <c r="AX172" s="16" t="n">
+        <v>1658.7</v>
+      </c>
+      <c r="AY172" s="16" t="n">
+        <v>1753.7</v>
+      </c>
+      <c r="AZ172" s="16" t="n">
+        <v>1548.8</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="14" t="inlineStr">
+        <is>
+          <t>Ramp Down Available (MW)</t>
+        </is>
+      </c>
+      <c r="B173" s="15" t="n"/>
+      <c r="C173" s="15" t="n"/>
+      <c r="D173" s="15" t="n"/>
+      <c r="E173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="16" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="G173" s="16" t="n">
+        <v>181</v>
+      </c>
+      <c r="H173" s="16" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="I173" s="16" t="n">
+        <v>378.6</v>
+      </c>
+      <c r="J173" s="16" t="n">
+        <v>665.2</v>
+      </c>
+      <c r="K173" s="16" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="L173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" s="16" t="n">
+        <v>260.1</v>
+      </c>
+      <c r="V173" s="16" t="n">
+        <v>614.6</v>
+      </c>
+      <c r="W173" s="16" t="n">
+        <v>452.7</v>
+      </c>
+      <c r="X173" s="16" t="n">
+        <v>310.1</v>
+      </c>
+      <c r="Y173" s="16" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="Z173" s="16" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="AA173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB173" s="16" t="n">
+        <v>233.2</v>
+      </c>
+      <c r="AC173" s="16" t="n">
+        <v>157.1</v>
+      </c>
+      <c r="AD173" s="16" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AE173" s="16" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="AF173" s="16" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="AG173" s="16" t="n">
+        <v>261.7</v>
+      </c>
+      <c r="AH173" s="16" t="n">
+        <v>346.4</v>
+      </c>
+      <c r="AI173" s="16" t="n">
+        <v>509</v>
+      </c>
+      <c r="AJ173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS173" s="16" t="n">
+        <v>738</v>
+      </c>
+      <c r="AT173" s="16" t="n">
+        <v>704.8</v>
+      </c>
+      <c r="AU173" s="16" t="n">
+        <v>608.5</v>
+      </c>
+      <c r="AV173" s="16" t="n">
+        <v>787.7</v>
+      </c>
+      <c r="AW173" s="16" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="AX173" s="16" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="AY173" s="16" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AZ173" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="14" t="inlineStr">
+        <is>
+          <t>Total Dispatch (MW)</t>
+        </is>
+      </c>
+      <c r="B174" s="15" t="n"/>
+      <c r="C174" s="15" t="n"/>
+      <c r="D174" s="15" t="n"/>
+      <c r="E174" s="16" t="n">
         <v>3941.7</v>
       </c>
-      <c r="F165" s="16" t="n">
+      <c r="F174" s="16" t="n">
         <v>3473.8</v>
       </c>
-      <c r="G165" s="16" t="n">
+      <c r="G174" s="16" t="n">
         <v>3481.1</v>
       </c>
-      <c r="H165" s="16" t="n">
+      <c r="H174" s="16" t="n">
         <v>3498.2</v>
       </c>
-      <c r="I165" s="16" t="n">
+      <c r="I174" s="16" t="n">
         <v>3656.7</v>
       </c>
-      <c r="J165" s="16" t="n">
+      <c r="J174" s="16" t="n">
         <v>3965.2</v>
       </c>
-      <c r="K165" s="16" t="n">
+      <c r="K174" s="16" t="n">
         <v>4403.8</v>
       </c>
-      <c r="L165" s="16" t="n">
+      <c r="L174" s="16" t="n">
         <v>2170</v>
       </c>
-      <c r="M165" s="16" t="n">
+      <c r="M174" s="16" t="n">
         <v>2589.4</v>
       </c>
-      <c r="N165" s="16" t="n">
+      <c r="N174" s="16" t="n">
         <v>2788.2</v>
       </c>
-      <c r="O165" s="16" t="n">
+      <c r="O174" s="16" t="n">
         <v>2916</v>
       </c>
-      <c r="P165" s="16" t="n">
+      <c r="P174" s="16" t="n">
         <v>3037.1</v>
       </c>
-      <c r="Q165" s="16" t="n">
+      <c r="Q174" s="16" t="n">
         <v>3046.6</v>
       </c>
-      <c r="R165" s="16" t="n">
+      <c r="R174" s="16" t="n">
         <v>2967.8</v>
       </c>
-      <c r="S165" s="16" t="n">
+      <c r="S174" s="16" t="n">
         <v>2776.4</v>
       </c>
-      <c r="T165" s="16" t="n">
+      <c r="T174" s="16" t="n">
         <v>2483.7</v>
       </c>
-      <c r="U165" s="16" t="n">
+      <c r="U174" s="16" t="n">
         <v>4381.8</v>
       </c>
-      <c r="V165" s="16" t="n">
+      <c r="V174" s="16" t="n">
         <v>4789.1</v>
       </c>
-      <c r="W165" s="16" t="n">
+      <c r="W174" s="16" t="n">
         <v>4848.5</v>
       </c>
-      <c r="X165" s="16" t="n">
+      <c r="X174" s="16" t="n">
         <v>4793.6</v>
       </c>
-      <c r="Y165" s="16" t="n">
+      <c r="Y174" s="16" t="n">
         <v>4636.3</v>
       </c>
-      <c r="Z165" s="16" t="n">
+      <c r="Z174" s="16" t="n">
         <v>4345.2</v>
       </c>
-      <c r="AA165" s="16" t="n">
+      <c r="AA174" s="16" t="n">
         <v>4353.7</v>
       </c>
-      <c r="AB165" s="16" t="n">
+      <c r="AB174" s="16" t="n">
         <v>3642.2</v>
       </c>
-      <c r="AC165" s="16" t="n">
+      <c r="AC174" s="16" t="n">
         <v>3426.7</v>
       </c>
-      <c r="AD165" s="16" t="n">
+      <c r="AD174" s="16" t="n">
         <v>3452</v>
       </c>
-      <c r="AE165" s="16" t="n">
+      <c r="AE174" s="16" t="n">
         <v>3439.3</v>
       </c>
-      <c r="AF165" s="16" t="n">
+      <c r="AF174" s="16" t="n">
         <v>3467.1</v>
       </c>
-      <c r="AG165" s="16" t="n">
+      <c r="AG174" s="16" t="n">
         <v>3614</v>
       </c>
-      <c r="AH165" s="16" t="n">
+      <c r="AH174" s="16" t="n">
         <v>3940.5</v>
       </c>
-      <c r="AI165" s="16" t="n">
+      <c r="AI174" s="16" t="n">
         <v>4228.3</v>
       </c>
-      <c r="AJ165" s="16" t="n">
+      <c r="AJ174" s="16" t="n">
         <v>2020.5</v>
       </c>
-      <c r="AK165" s="16" t="n">
+      <c r="AK174" s="16" t="n">
         <v>2356.6</v>
       </c>
-      <c r="AL165" s="16" t="n">
+      <c r="AL174" s="16" t="n">
         <v>2524.3</v>
       </c>
-      <c r="AM165" s="16" t="n">
+      <c r="AM174" s="16" t="n">
         <v>2625.3</v>
       </c>
-      <c r="AN165" s="16" t="n">
+      <c r="AN174" s="16" t="n">
         <v>2440.6</v>
       </c>
-      <c r="AO165" s="16" t="n">
+      <c r="AO174" s="16" t="n">
         <v>2260.2</v>
       </c>
-      <c r="AP165" s="16" t="n">
+      <c r="AP174" s="16" t="n">
         <v>2261.1</v>
       </c>
-      <c r="AQ165" s="16" t="n">
+      <c r="AQ174" s="16" t="n">
         <v>2130.7</v>
       </c>
-      <c r="AR165" s="16" t="n">
+      <c r="AR174" s="16" t="n">
         <v>1973.4</v>
       </c>
-      <c r="AS165" s="16" t="n">
+      <c r="AS174" s="16" t="n">
         <v>4285.6</v>
       </c>
-      <c r="AT165" s="16" t="n">
+      <c r="AT174" s="16" t="n">
         <v>4673.1</v>
       </c>
-      <c r="AU165" s="16" t="n">
+      <c r="AU174" s="16" t="n">
         <v>4695.7</v>
       </c>
-      <c r="AV165" s="16" t="n">
+      <c r="AV174" s="16" t="n">
         <v>4608.5</v>
       </c>
-      <c r="AW165" s="16" t="n">
+      <c r="AW174" s="16" t="n">
         <v>4447.1</v>
       </c>
-      <c r="AX165" s="16" t="n">
+      <c r="AX174" s="16" t="n">
         <v>4163.5</v>
       </c>
-      <c r="AY165" s="16" t="n">
+      <c r="AY174" s="16" t="n">
         <v>3789.5</v>
       </c>
-      <c r="AZ165" s="16" t="n">
+      <c r="AZ174" s="16" t="n">
         <v>3725</v>
       </c>
     </row>
